--- a/基差监控实时数据.xlsx
+++ b/基差监控实时数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -479,20 +479,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>剩余交易日</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>基差(期-现)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>基差点比</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>年化(交易日)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>年化(自然日)</t>
         </is>
@@ -510,31 +515,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4934.8</v>
+        <v>4952.6</v>
       </c>
       <c r="D2" t="n">
-        <v>4939.21</v>
+        <v>4950.74</v>
       </c>
       <c r="E2" t="n">
         <v>53</v>
       </c>
       <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="H2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.0566</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-4.41</v>
-      </c>
       <c r="I2" t="n">
-        <v>-8.93</v>
+        <v>1.86</v>
       </c>
       <c r="J2" t="n">
-        <v>-370.44</v>
+        <v>3.76</v>
       </c>
       <c r="K2" t="n">
-        <v>-536.55</v>
+        <v>156.24</v>
+      </c>
+      <c r="L2" t="n">
+        <v>339.45</v>
       </c>
     </row>
     <row r="3">
@@ -549,31 +557,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4902.2</v>
+        <v>4921.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4939.21</v>
+        <v>4950.74</v>
       </c>
       <c r="E3" t="n">
         <v>245</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1673</v>
+        <v>0.1633</v>
       </c>
       <c r="H3" t="n">
-        <v>-37.01</v>
+        <v>28</v>
       </c>
       <c r="I3" t="n">
-        <v>-74.93000000000001</v>
+        <v>-29.34</v>
       </c>
       <c r="J3" t="n">
-        <v>-227.48</v>
+        <v>-59.26</v>
       </c>
       <c r="K3" t="n">
-        <v>-329.48</v>
+        <v>-264.06</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-267.73</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +599,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4831</v>
+        <v>4850.2</v>
       </c>
       <c r="D4" t="n">
-        <v>4939.21</v>
+        <v>4950.74</v>
       </c>
       <c r="E4" t="n">
         <v>242</v>
       </c>
       <c r="F4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5331</v>
+        <v>0.5289</v>
       </c>
       <c r="H4" t="n">
-        <v>-108.21</v>
+        <v>92</v>
       </c>
       <c r="I4" t="n">
-        <v>-219.08</v>
+        <v>-100.54</v>
       </c>
       <c r="J4" t="n">
-        <v>-211.39</v>
+        <v>-203.08</v>
       </c>
       <c r="K4" t="n">
-        <v>-306.18</v>
+        <v>-275.39</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-286.7</v>
       </c>
     </row>
     <row r="5">
@@ -627,31 +641,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4782.4</v>
+        <v>4801.4</v>
       </c>
       <c r="D5" t="n">
-        <v>4939.21</v>
+        <v>4950.74</v>
       </c>
       <c r="E5" t="n">
         <v>242</v>
       </c>
       <c r="F5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9091</v>
+        <v>0.905</v>
       </c>
       <c r="H5" t="n">
-        <v>-156.81</v>
+        <v>151</v>
       </c>
       <c r="I5" t="n">
-        <v>-317.48</v>
+        <v>-149.34</v>
       </c>
       <c r="J5" t="n">
-        <v>-179.62</v>
+        <v>-301.65</v>
       </c>
       <c r="K5" t="n">
-        <v>-260.16</v>
+        <v>-249.23</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-248.9</v>
       </c>
     </row>
     <row r="6">
@@ -666,31 +683,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3035.6</v>
+        <v>3027.8</v>
       </c>
       <c r="D6" t="n">
-        <v>3038.89</v>
+        <v>3026.03</v>
       </c>
       <c r="E6" t="n">
         <v>53</v>
       </c>
       <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="H6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.0566</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-3.29</v>
-      </c>
       <c r="I6" t="n">
-        <v>-10.83</v>
+        <v>1.77</v>
       </c>
       <c r="J6" t="n">
-        <v>-276.36</v>
+        <v>5.85</v>
       </c>
       <c r="K6" t="n">
-        <v>-400.28</v>
+        <v>148.68</v>
+      </c>
+      <c r="L6" t="n">
+        <v>323.02</v>
       </c>
     </row>
     <row r="7">
@@ -705,31 +725,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3019.6</v>
+        <v>3014.2</v>
       </c>
       <c r="D7" t="n">
-        <v>3038.89</v>
+        <v>3026.03</v>
       </c>
       <c r="E7" t="n">
         <v>245</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1673</v>
+        <v>0.1633</v>
       </c>
       <c r="H7" t="n">
-        <v>-19.29</v>
+        <v>28</v>
       </c>
       <c r="I7" t="n">
-        <v>-63.48</v>
+        <v>-11.83</v>
       </c>
       <c r="J7" t="n">
-        <v>-118.56</v>
+        <v>-39.09</v>
       </c>
       <c r="K7" t="n">
-        <v>-171.73</v>
+        <v>-106.47</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-107.95</v>
       </c>
     </row>
     <row r="8">
@@ -744,31 +767,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2984.8</v>
+        <v>2981.8</v>
       </c>
       <c r="D8" t="n">
-        <v>3038.89</v>
+        <v>3026.03</v>
       </c>
       <c r="E8" t="n">
         <v>242</v>
       </c>
       <c r="F8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5331</v>
+        <v>0.5289</v>
       </c>
       <c r="H8" t="n">
-        <v>-54.09</v>
+        <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>-177.99</v>
+        <v>-44.23</v>
       </c>
       <c r="J8" t="n">
-        <v>-105.66</v>
+        <v>-146.17</v>
       </c>
       <c r="K8" t="n">
-        <v>-153.05</v>
+        <v>-121.15</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-126.12</v>
       </c>
     </row>
     <row r="9">
@@ -783,31 +809,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2974.4</v>
+        <v>2969.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3038.89</v>
+        <v>3026.03</v>
       </c>
       <c r="E9" t="n">
         <v>242</v>
       </c>
       <c r="F9" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9091</v>
+        <v>0.905</v>
       </c>
       <c r="H9" t="n">
-        <v>-64.48999999999999</v>
+        <v>151</v>
       </c>
       <c r="I9" t="n">
-        <v>-212.22</v>
+        <v>-56.63</v>
       </c>
       <c r="J9" t="n">
-        <v>-73.87</v>
+        <v>-187.14</v>
       </c>
       <c r="K9" t="n">
-        <v>-106.99</v>
+        <v>-94.51000000000001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-94.38</v>
       </c>
     </row>
     <row r="10">
@@ -822,31 +851,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8761.799999999999</v>
+        <v>8813.799999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>8762.85</v>
+        <v>8812.139999999999</v>
       </c>
       <c r="E10" t="n">
         <v>53</v>
       </c>
       <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0566</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-1.05</v>
-      </c>
       <c r="I10" t="n">
-        <v>-1.2</v>
+        <v>1.66</v>
       </c>
       <c r="J10" t="n">
-        <v>-88.2</v>
+        <v>1.88</v>
       </c>
       <c r="K10" t="n">
-        <v>-127.75</v>
+        <v>139.44</v>
+      </c>
+      <c r="L10" t="n">
+        <v>302.95</v>
       </c>
     </row>
     <row r="11">
@@ -861,31 +893,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8686</v>
+        <v>8739</v>
       </c>
       <c r="D11" t="n">
-        <v>8762.85</v>
+        <v>8812.139999999999</v>
       </c>
       <c r="E11" t="n">
         <v>245</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1673</v>
+        <v>0.1633</v>
       </c>
       <c r="H11" t="n">
-        <v>-76.84999999999999</v>
+        <v>28</v>
       </c>
       <c r="I11" t="n">
-        <v>-87.7</v>
+        <v>-73.14</v>
       </c>
       <c r="J11" t="n">
-        <v>-472.35</v>
+        <v>-83</v>
       </c>
       <c r="K11" t="n">
-        <v>-684.15</v>
+        <v>-658.26</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-667.4</v>
       </c>
     </row>
     <row r="12">
@@ -900,31 +935,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8549</v>
+        <v>8598</v>
       </c>
       <c r="D12" t="n">
-        <v>8762.85</v>
+        <v>8812.139999999999</v>
       </c>
       <c r="E12" t="n">
         <v>242</v>
       </c>
       <c r="F12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5331</v>
+        <v>0.5289</v>
       </c>
       <c r="H12" t="n">
-        <v>-213.85</v>
+        <v>92</v>
       </c>
       <c r="I12" t="n">
-        <v>-244.04</v>
+        <v>-214.14</v>
       </c>
       <c r="J12" t="n">
-        <v>-417.75</v>
+        <v>-243.01</v>
       </c>
       <c r="K12" t="n">
-        <v>-605.08</v>
+        <v>-586.5599999999999</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-610.63</v>
       </c>
     </row>
     <row r="13">
@@ -939,31 +977,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8418.200000000001</v>
+        <v>8464.200000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>8762.85</v>
+        <v>8812.139999999999</v>
       </c>
       <c r="E13" t="n">
         <v>242</v>
       </c>
       <c r="F13" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9091</v>
+        <v>0.905</v>
       </c>
       <c r="H13" t="n">
-        <v>-344.65</v>
+        <v>151</v>
       </c>
       <c r="I13" t="n">
-        <v>-393.31</v>
+        <v>-347.94</v>
       </c>
       <c r="J13" t="n">
-        <v>-394.78</v>
+        <v>-394.84</v>
       </c>
       <c r="K13" t="n">
-        <v>-571.8099999999999</v>
+        <v>-580.67</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-579.9</v>
       </c>
     </row>
     <row r="14">
@@ -978,31 +1019,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8782.6</v>
+        <v>8860.200000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>8791.540000000001</v>
+        <v>8861.9</v>
       </c>
       <c r="E14" t="n">
         <v>53</v>
       </c>
       <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="H14" t="n">
         <v>3</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.0566</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-8.94</v>
-      </c>
       <c r="I14" t="n">
-        <v>-10.17</v>
+        <v>-1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>-750.96</v>
+        <v>-1.92</v>
       </c>
       <c r="K14" t="n">
-        <v>-1087.7</v>
+        <v>-142.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-310.25</v>
       </c>
     </row>
     <row r="15">
@@ -1017,31 +1061,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8688.799999999999</v>
+        <v>8769</v>
       </c>
       <c r="D15" t="n">
-        <v>8791.540000000001</v>
+        <v>8861.9</v>
       </c>
       <c r="E15" t="n">
         <v>245</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1673</v>
+        <v>0.1633</v>
       </c>
       <c r="H15" t="n">
-        <v>-102.74</v>
+        <v>28</v>
       </c>
       <c r="I15" t="n">
-        <v>-116.86</v>
+        <v>-92.90000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-631.48</v>
+        <v>-104.83</v>
       </c>
       <c r="K15" t="n">
-        <v>-914.64</v>
+        <v>-836.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-847.71</v>
       </c>
     </row>
     <row r="16">
@@ -1056,31 +1103,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8478.4</v>
+        <v>8558.6</v>
       </c>
       <c r="D16" t="n">
-        <v>8791.540000000001</v>
+        <v>8861.9</v>
       </c>
       <c r="E16" t="n">
         <v>242</v>
       </c>
       <c r="F16" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5331</v>
+        <v>0.5289</v>
       </c>
       <c r="H16" t="n">
-        <v>-313.14</v>
+        <v>92</v>
       </c>
       <c r="I16" t="n">
-        <v>-356.18</v>
+        <v>-303.3</v>
       </c>
       <c r="J16" t="n">
-        <v>-611.72</v>
+        <v>-342.25</v>
       </c>
       <c r="K16" t="n">
-        <v>-886.02</v>
+        <v>-830.78</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-864.88</v>
       </c>
     </row>
     <row r="17">
@@ -1095,31 +1145,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8292</v>
+        <v>8370</v>
       </c>
       <c r="D17" t="n">
-        <v>8791.540000000001</v>
+        <v>8861.9</v>
       </c>
       <c r="E17" t="n">
         <v>242</v>
       </c>
       <c r="F17" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9091</v>
+        <v>0.905</v>
       </c>
       <c r="H17" t="n">
-        <v>-499.54</v>
+        <v>151</v>
       </c>
       <c r="I17" t="n">
-        <v>-568.21</v>
+        <v>-491.9</v>
       </c>
       <c r="J17" t="n">
-        <v>-572.2</v>
+        <v>-555.0700000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-828.78</v>
+        <v>-820.92</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-819.83</v>
       </c>
     </row>
   </sheetData>

--- a/基差监控实时数据.xlsx
+++ b/基差监控实时数据.xlsx
@@ -435,10 +435,11 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,10 +516,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4940.6</v>
+        <v>4937.4</v>
       </c>
       <c r="D2" t="n">
-        <v>4942.03</v>
+        <v>4939.08</v>
       </c>
       <c r="E2" t="n">
         <v>53</v>
@@ -533,16 +534,16 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.43</v>
+        <v>-1.68</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.89</v>
+        <v>-3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>-120.12</v>
+        <v>-141.12</v>
       </c>
       <c r="L2" t="n">
-        <v>-260.97</v>
+        <v>-306.6</v>
       </c>
     </row>
     <row r="3">
@@ -557,10 +558,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4909</v>
+        <v>4906.2</v>
       </c>
       <c r="D3" t="n">
-        <v>4942.03</v>
+        <v>4939.08</v>
       </c>
       <c r="E3" t="n">
         <v>245</v>
@@ -575,16 +576,16 @@
         <v>28</v>
       </c>
       <c r="I3" t="n">
-        <v>-33.03</v>
+        <v>-32.88</v>
       </c>
       <c r="J3" t="n">
-        <v>-66.83</v>
+        <v>-66.56999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-297.27</v>
+        <v>-295.92</v>
       </c>
       <c r="L3" t="n">
-        <v>-301.4</v>
+        <v>-300.03</v>
       </c>
     </row>
     <row r="4">
@@ -599,10 +600,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4838.8</v>
+        <v>4834.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4942.03</v>
+        <v>4939.08</v>
       </c>
       <c r="E4" t="n">
         <v>242</v>
@@ -617,16 +618,16 @@
         <v>92</v>
       </c>
       <c r="I4" t="n">
-        <v>-103.23</v>
+        <v>-104.68</v>
       </c>
       <c r="J4" t="n">
-        <v>-208.88</v>
+        <v>-211.94</v>
       </c>
       <c r="K4" t="n">
-        <v>-282.76</v>
+        <v>-286.73</v>
       </c>
       <c r="L4" t="n">
-        <v>-294.37</v>
+        <v>-298.5</v>
       </c>
     </row>
     <row r="5">
@@ -641,10 +642,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4790.4</v>
+        <v>4788</v>
       </c>
       <c r="D5" t="n">
-        <v>4942.03</v>
+        <v>4939.08</v>
       </c>
       <c r="E5" t="n">
         <v>242</v>
@@ -659,16 +660,16 @@
         <v>151</v>
       </c>
       <c r="I5" t="n">
-        <v>-151.63</v>
+        <v>-151.08</v>
       </c>
       <c r="J5" t="n">
-        <v>-306.82</v>
+        <v>-305.89</v>
       </c>
       <c r="K5" t="n">
-        <v>-253.05</v>
+        <v>-252.13</v>
       </c>
       <c r="L5" t="n">
-        <v>-252.72</v>
+        <v>-251.8</v>
       </c>
     </row>
     <row r="6">
@@ -683,10 +684,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3022.8</v>
+        <v>3021.2</v>
       </c>
       <c r="D6" t="n">
-        <v>3023.02</v>
+        <v>3020.9</v>
       </c>
       <c r="E6" t="n">
         <v>53</v>
@@ -701,16 +702,16 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.22</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.73</v>
+        <v>0.99</v>
       </c>
       <c r="K6" t="n">
-        <v>-18.48</v>
+        <v>25.2</v>
       </c>
       <c r="L6" t="n">
-        <v>-40.15</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="7">
@@ -725,10 +726,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3008.8</v>
+        <v>3006.8</v>
       </c>
       <c r="D7" t="n">
-        <v>3023.02</v>
+        <v>3020.9</v>
       </c>
       <c r="E7" t="n">
         <v>245</v>
@@ -743,16 +744,16 @@
         <v>28</v>
       </c>
       <c r="I7" t="n">
-        <v>-14.22</v>
+        <v>-14.1</v>
       </c>
       <c r="J7" t="n">
-        <v>-47.04</v>
+        <v>-46.67</v>
       </c>
       <c r="K7" t="n">
-        <v>-127.98</v>
+        <v>-126.9</v>
       </c>
       <c r="L7" t="n">
-        <v>-129.76</v>
+        <v>-128.66</v>
       </c>
     </row>
     <row r="8">
@@ -767,10 +768,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2976.2</v>
+        <v>2974</v>
       </c>
       <c r="D8" t="n">
-        <v>3023.02</v>
+        <v>3020.9</v>
       </c>
       <c r="E8" t="n">
         <v>242</v>
@@ -785,16 +786,16 @@
         <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>-46.82</v>
+        <v>-46.9</v>
       </c>
       <c r="J8" t="n">
-        <v>-154.88</v>
+        <v>-155.25</v>
       </c>
       <c r="K8" t="n">
-        <v>-128.25</v>
+        <v>-128.47</v>
       </c>
       <c r="L8" t="n">
-        <v>-133.51</v>
+        <v>-133.74</v>
       </c>
     </row>
     <row r="9">
@@ -809,10 +810,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2964.2</v>
+        <v>2961</v>
       </c>
       <c r="D9" t="n">
-        <v>3023.02</v>
+        <v>3020.9</v>
       </c>
       <c r="E9" t="n">
         <v>242</v>
@@ -827,16 +828,16 @@
         <v>151</v>
       </c>
       <c r="I9" t="n">
-        <v>-58.82</v>
+        <v>-59.9</v>
       </c>
       <c r="J9" t="n">
-        <v>-194.57</v>
+        <v>-198.29</v>
       </c>
       <c r="K9" t="n">
-        <v>-98.16</v>
+        <v>-99.97</v>
       </c>
       <c r="L9" t="n">
-        <v>-98.03</v>
+        <v>-99.83</v>
       </c>
     </row>
     <row r="10">
@@ -851,10 +852,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8800.6</v>
+        <v>8795.200000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>8806.83</v>
+        <v>8803.73</v>
       </c>
       <c r="E10" t="n">
         <v>53</v>
@@ -869,16 +870,16 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.23</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.07</v>
+        <v>-9.69</v>
       </c>
       <c r="K10" t="n">
-        <v>-523.3200000000001</v>
+        <v>-716.52</v>
       </c>
       <c r="L10" t="n">
-        <v>-1136.97</v>
+        <v>-1556.72</v>
       </c>
     </row>
     <row r="11">
@@ -893,10 +894,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8723.200000000001</v>
+        <v>8718.6</v>
       </c>
       <c r="D11" t="n">
-        <v>8806.83</v>
+        <v>8803.73</v>
       </c>
       <c r="E11" t="n">
         <v>245</v>
@@ -911,16 +912,16 @@
         <v>28</v>
       </c>
       <c r="I11" t="n">
-        <v>-83.63</v>
+        <v>-85.13</v>
       </c>
       <c r="J11" t="n">
-        <v>-94.95999999999999</v>
+        <v>-96.7</v>
       </c>
       <c r="K11" t="n">
-        <v>-752.67</v>
+        <v>-766.17</v>
       </c>
       <c r="L11" t="n">
-        <v>-763.12</v>
+        <v>-776.8099999999999</v>
       </c>
     </row>
     <row r="12">
@@ -935,10 +936,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8581.6</v>
+        <v>8574.799999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>8806.83</v>
+        <v>8803.73</v>
       </c>
       <c r="E12" t="n">
         <v>242</v>
@@ -953,16 +954,16 @@
         <v>92</v>
       </c>
       <c r="I12" t="n">
-        <v>-225.23</v>
+        <v>-228.93</v>
       </c>
       <c r="J12" t="n">
-        <v>-255.74</v>
+        <v>-260.04</v>
       </c>
       <c r="K12" t="n">
-        <v>-616.9299999999999</v>
+        <v>-627.0700000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-642.26</v>
+        <v>-652.8099999999999</v>
       </c>
     </row>
     <row r="13">
@@ -977,10 +978,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8447.6</v>
+        <v>8441.200000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>8806.83</v>
+        <v>8803.73</v>
       </c>
       <c r="E13" t="n">
         <v>242</v>
@@ -995,16 +996,16 @@
         <v>151</v>
       </c>
       <c r="I13" t="n">
-        <v>-359.23</v>
+        <v>-362.53</v>
       </c>
       <c r="J13" t="n">
-        <v>-407.9</v>
+        <v>-411.79</v>
       </c>
       <c r="K13" t="n">
-        <v>-599.51</v>
+        <v>-605.02</v>
       </c>
       <c r="L13" t="n">
-        <v>-598.72</v>
+        <v>-604.22</v>
       </c>
     </row>
     <row r="14">
@@ -1019,10 +1020,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8846.200000000001</v>
+        <v>8844.799999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>8859.18</v>
+        <v>8858.110000000001</v>
       </c>
       <c r="E14" t="n">
         <v>53</v>
@@ -1037,16 +1038,16 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.98</v>
+        <v>-13.31</v>
       </c>
       <c r="J14" t="n">
-        <v>-14.65</v>
+        <v>-15.03</v>
       </c>
       <c r="K14" t="n">
-        <v>-1090.32</v>
+        <v>-1118.04</v>
       </c>
       <c r="L14" t="n">
-        <v>-2368.85</v>
+        <v>-2429.08</v>
       </c>
     </row>
     <row r="15">
@@ -1061,10 +1062,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8752.6</v>
+        <v>8749.4</v>
       </c>
       <c r="D15" t="n">
-        <v>8859.18</v>
+        <v>8858.110000000001</v>
       </c>
       <c r="E15" t="n">
         <v>245</v>
@@ -1079,16 +1080,16 @@
         <v>28</v>
       </c>
       <c r="I15" t="n">
-        <v>-106.58</v>
+        <v>-108.71</v>
       </c>
       <c r="J15" t="n">
-        <v>-120.3</v>
+        <v>-122.72</v>
       </c>
       <c r="K15" t="n">
-        <v>-959.22</v>
+        <v>-978.39</v>
       </c>
       <c r="L15" t="n">
-        <v>-972.54</v>
+        <v>-991.98</v>
       </c>
     </row>
     <row r="16">
@@ -1103,10 +1104,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8542.6</v>
+        <v>8538.6</v>
       </c>
       <c r="D16" t="n">
-        <v>8859.18</v>
+        <v>8858.110000000001</v>
       </c>
       <c r="E16" t="n">
         <v>242</v>
@@ -1121,16 +1122,16 @@
         <v>92</v>
       </c>
       <c r="I16" t="n">
-        <v>-316.58</v>
+        <v>-319.51</v>
       </c>
       <c r="J16" t="n">
-        <v>-357.35</v>
+        <v>-360.7</v>
       </c>
       <c r="K16" t="n">
-        <v>-867.15</v>
+        <v>-875.1799999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-902.75</v>
+        <v>-911.1</v>
       </c>
     </row>
     <row r="17">
@@ -1145,10 +1146,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8354.4</v>
+        <v>8349</v>
       </c>
       <c r="D17" t="n">
-        <v>8859.18</v>
+        <v>8858.110000000001</v>
       </c>
       <c r="E17" t="n">
         <v>242</v>
@@ -1163,16 +1164,16 @@
         <v>151</v>
       </c>
       <c r="I17" t="n">
-        <v>-504.78</v>
+        <v>-509.11</v>
       </c>
       <c r="J17" t="n">
-        <v>-569.78</v>
+        <v>-574.74</v>
       </c>
       <c r="K17" t="n">
-        <v>-842.41</v>
+        <v>-849.64</v>
       </c>
       <c r="L17" t="n">
-        <v>-841.3</v>
+        <v>-848.52</v>
       </c>
     </row>
   </sheetData>

--- a/基差监控实时数据.xlsx
+++ b/基差监控实时数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -465,40 +465,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>价差差值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>合约总天数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>剩余天数</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>剩余天数占比</t>
+          <t>剩余交易日</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>剩余交易日</t>
+          <t>基差(期-现)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>基差(期-现)</t>
+          <t>年化(交易日)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>基差点比</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>年化(交易日)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>年化(自然日)</t>
         </is>
@@ -516,34 +506,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4937.4</v>
+        <v>4940.4</v>
       </c>
       <c r="D2" t="n">
-        <v>4939.08</v>
-      </c>
-      <c r="E2" t="n">
-        <v>53</v>
-      </c>
+        <v>4944.27</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.0377</v>
-      </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>-3.87</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.68</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-141.12</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-306.6</v>
+        <v>-28.57</v>
       </c>
     </row>
     <row r="3">
@@ -558,34 +540,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4906.2</v>
+        <v>4904.8</v>
       </c>
       <c r="D3" t="n">
-        <v>4939.08</v>
+        <v>4944.27</v>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>35.6</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1633</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>-39.47</v>
       </c>
       <c r="I3" t="n">
-        <v>-32.88</v>
+        <v>-7.45</v>
       </c>
       <c r="J3" t="n">
-        <v>-66.56999999999999</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-295.92</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-300.03</v>
+        <v>-7.47</v>
       </c>
     </row>
     <row r="4">
@@ -600,34 +576,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4834.4</v>
+        <v>4832.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4939.08</v>
+        <v>4944.27</v>
       </c>
       <c r="E4" t="n">
-        <v>242</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5289</v>
+        <v>91</v>
       </c>
       <c r="H4" t="n">
-        <v>92</v>
+        <v>-111.87</v>
       </c>
       <c r="I4" t="n">
-        <v>-104.68</v>
+        <v>-6.27</v>
       </c>
       <c r="J4" t="n">
-        <v>-211.94</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-286.73</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-298.5</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="5">
@@ -642,538 +612,454 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4788</v>
+        <v>4781.8</v>
       </c>
       <c r="D5" t="n">
-        <v>4939.08</v>
+        <v>4944.27</v>
       </c>
       <c r="E5" t="n">
-        <v>242</v>
+        <v>50.6</v>
       </c>
       <c r="F5" t="n">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="G5" t="n">
-        <v>0.905</v>
+        <v>150</v>
       </c>
       <c r="H5" t="n">
-        <v>151</v>
+        <v>-162.47</v>
       </c>
       <c r="I5" t="n">
-        <v>-151.08</v>
+        <v>-5.52</v>
       </c>
       <c r="J5" t="n">
-        <v>-305.89</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-252.13</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-251.8</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IH2605</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>上证50 2605</t>
+          <t>中证500 2605</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3021.2</v>
+        <v>8726</v>
       </c>
       <c r="D6" t="n">
-        <v>3020.9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>53</v>
-      </c>
+        <v>8733.09</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.0377</v>
-      </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>-7.09</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>-10.23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="K6" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>54.75</v>
+        <v>-29.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IH2606</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>上证50 2606</t>
+          <t>中证500 2606</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3006.8</v>
+        <v>8651.6</v>
       </c>
       <c r="D7" t="n">
-        <v>3020.9</v>
+        <v>8733.09</v>
       </c>
       <c r="E7" t="n">
-        <v>245</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1633</v>
+        <v>27</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>-81.48999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-14.1</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-46.67</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-126.9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-128.66</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IH2609</t>
+          <t>IC2609</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>上证50 2609</t>
+          <t>中证500 2609</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2974</v>
+        <v>8509.200000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>3020.9</v>
+        <v>8733.09</v>
       </c>
       <c r="E8" t="n">
-        <v>242</v>
+        <v>142.4</v>
       </c>
       <c r="F8" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5289</v>
+        <v>91</v>
       </c>
       <c r="H8" t="n">
-        <v>92</v>
+        <v>-223.89</v>
       </c>
       <c r="I8" t="n">
-        <v>-46.9</v>
+        <v>-7.1</v>
       </c>
       <c r="J8" t="n">
-        <v>-155.25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-128.47</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-133.74</v>
+        <v>-7.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IH2612</t>
+          <t>IC2612</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>上证50 2612</t>
+          <t>中证500 2612</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2961</v>
+        <v>8380.200000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>3020.9</v>
+        <v>8733.09</v>
       </c>
       <c r="E9" t="n">
-        <v>242</v>
+        <v>129</v>
       </c>
       <c r="F9" t="n">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="G9" t="n">
-        <v>0.905</v>
+        <v>150</v>
       </c>
       <c r="H9" t="n">
-        <v>151</v>
+        <v>-352.89</v>
       </c>
       <c r="I9" t="n">
-        <v>-59.9</v>
+        <v>-6.79</v>
       </c>
       <c r="J9" t="n">
-        <v>-198.29</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-99.97</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-99.83</v>
+        <v>-6.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IM2605</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中证500 2605</t>
+          <t>中证1000 2605</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8795.200000000001</v>
+        <v>8820.200000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>8803.73</v>
-      </c>
-      <c r="E10" t="n">
-        <v>53</v>
-      </c>
+        <v>8830.49</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0377</v>
-      </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>-10.29</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.529999999999999</v>
+        <v>-14.68</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.69</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-716.52</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1556.72</v>
+        <v>-42.53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IM2606</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中证500 2606</t>
+          <t>中证1000 2606</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8718.6</v>
+        <v>8725.4</v>
       </c>
       <c r="D11" t="n">
-        <v>8803.73</v>
+        <v>8830.49</v>
       </c>
       <c r="E11" t="n">
-        <v>245</v>
+        <v>94.8</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1633</v>
+        <v>27</v>
       </c>
       <c r="H11" t="n">
-        <v>28</v>
+        <v>-105.09</v>
       </c>
       <c r="I11" t="n">
-        <v>-85.13</v>
+        <v>-11.11</v>
       </c>
       <c r="J11" t="n">
-        <v>-96.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-766.17</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-776.8099999999999</v>
+        <v>-11.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC2609</t>
+          <t>IM2609</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中证500 2609</t>
+          <t>中证1000 2609</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8574.799999999999</v>
+        <v>8519</v>
       </c>
       <c r="D12" t="n">
-        <v>8803.73</v>
+        <v>8830.49</v>
       </c>
       <c r="E12" t="n">
-        <v>242</v>
+        <v>206.4</v>
       </c>
       <c r="F12" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5289</v>
+        <v>91</v>
       </c>
       <c r="H12" t="n">
-        <v>92</v>
+        <v>-311.49</v>
       </c>
       <c r="I12" t="n">
-        <v>-228.93</v>
+        <v>-9.77</v>
       </c>
       <c r="J12" t="n">
-        <v>-260.04</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-627.0700000000001</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-652.8099999999999</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC2612</t>
+          <t>IM2612</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中证500 2612</t>
+          <t>中证1000 2612</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8441.200000000001</v>
+        <v>8336</v>
       </c>
       <c r="D13" t="n">
-        <v>8803.73</v>
+        <v>8830.49</v>
       </c>
       <c r="E13" t="n">
-        <v>242</v>
+        <v>183</v>
       </c>
       <c r="F13" t="n">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="G13" t="n">
-        <v>0.905</v>
+        <v>150</v>
       </c>
       <c r="H13" t="n">
-        <v>151</v>
+        <v>-494.49</v>
       </c>
       <c r="I13" t="n">
-        <v>-362.53</v>
+        <v>-9.41</v>
       </c>
       <c r="J13" t="n">
-        <v>-411.79</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-605.02</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-604.22</v>
+        <v>-9.380000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IM2605</t>
+          <t>IH2605</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中证1000 2605</t>
+          <t>上证50 2605</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8844.799999999999</v>
+        <v>3017.2</v>
       </c>
       <c r="D14" t="n">
-        <v>8858.110000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>53</v>
-      </c>
+        <v>3020.02</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.0377</v>
-      </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>-2.82</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.31</v>
+        <v>-11.77</v>
       </c>
       <c r="J14" t="n">
-        <v>-15.03</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-1118.04</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-2429.08</v>
+        <v>-34.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IM2606</t>
+          <t>IH2606</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中证1000 2606</t>
+          <t>上证50 2606</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8749.4</v>
+        <v>3002.4</v>
       </c>
       <c r="D15" t="n">
-        <v>8858.110000000001</v>
+        <v>3020.02</v>
       </c>
       <c r="E15" t="n">
-        <v>245</v>
+        <v>14.8</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1633</v>
+        <v>27</v>
       </c>
       <c r="H15" t="n">
-        <v>28</v>
+        <v>-17.62</v>
       </c>
       <c r="I15" t="n">
-        <v>-108.71</v>
+        <v>-5.45</v>
       </c>
       <c r="J15" t="n">
-        <v>-122.72</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-978.39</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-991.98</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IM2609</t>
+          <t>IH2609</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中证1000 2609</t>
+          <t>上证50 2609</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8538.6</v>
+        <v>2970.6</v>
       </c>
       <c r="D16" t="n">
-        <v>8858.110000000001</v>
+        <v>3020.02</v>
       </c>
       <c r="E16" t="n">
-        <v>242</v>
+        <v>31.8</v>
       </c>
       <c r="F16" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5289</v>
+        <v>91</v>
       </c>
       <c r="H16" t="n">
-        <v>92</v>
+        <v>-49.42</v>
       </c>
       <c r="I16" t="n">
-        <v>-319.51</v>
+        <v>-4.53</v>
       </c>
       <c r="J16" t="n">
-        <v>-360.7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-875.1799999999999</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-911.1</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IM2612</t>
+          <t>IH2612</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中证1000 2612</t>
+          <t>上证50 2612</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8349</v>
+        <v>2959.6</v>
       </c>
       <c r="D17" t="n">
-        <v>8858.110000000001</v>
+        <v>3020.02</v>
       </c>
       <c r="E17" t="n">
-        <v>242</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="G17" t="n">
-        <v>0.905</v>
+        <v>150</v>
       </c>
       <c r="H17" t="n">
-        <v>151</v>
+        <v>-60.42</v>
       </c>
       <c r="I17" t="n">
-        <v>-509.11</v>
+        <v>-3.36</v>
       </c>
       <c r="J17" t="n">
-        <v>-574.74</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-849.64</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-848.52</v>
+        <v>-3.35</v>
       </c>
     </row>
   </sheetData>
